--- a/data/historico/semanas_322-326.xlsx
+++ b/data/historico/semanas_322-326.xlsx
@@ -31,7 +31,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Visitas Acima de 20min'!$A$2:$J$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Fora do Expediente'!$A$2:$K$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Visitas no Almoço'!$A$2:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ausências'!$A$2:$G$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Cronograma'!$A$2:$D$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ponto Estratégico'!$A$2:$AE$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Resumo Semanal'!$A$2:$AE$81</definedName>
@@ -2914,16 +2914,16 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>29.6</v>
+        <v>28</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="H21" s="4" t="n">
         <v>5</v>
@@ -2932,7 +2932,7 @@
         <v>6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.05</v>
+        <v>3.57</v>
       </c>
       <c r="K21" s="4" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -2956,29 +2956,29 @@
         <v>0</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="S21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>22.11</v>
+        <v>21.13</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>5.04</v>
+        <v>4.92</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>12.6</v>
+        <v>14.78</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="Y21" s="4" t="inlineStr">
         <is>
-          <t>R$ 88,54</t>
+          <t>R$ 92,53</t>
         </is>
       </c>
       <c r="Z21" s="4" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="AB21" s="4" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AC21" s="4" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:14</t>
         </is>
       </c>
     </row>
@@ -5006,16 +5006,16 @@
         </is>
       </c>
       <c r="D41" s="4" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>22.29</v>
+        <v>22.5</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
       <c r="H41" s="4" t="n">
         <v>7</v>
@@ -5024,7 +5024,7 @@
         <v>11</v>
       </c>
       <c r="J41" s="4" t="n">
-        <v>7.05</v>
+        <v>6.11</v>
       </c>
       <c r="K41" s="4" t="n">
         <v>0</v>
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="M41" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
@@ -5048,39 +5048,39 @@
         <v>5</v>
       </c>
       <c r="R41" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="S41" s="4" t="n">
         <v>1</v>
       </c>
       <c r="T41" s="4" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>25.71</v>
+        <v>23.4</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>6.01</v>
+        <v>5.66</v>
       </c>
       <c r="W41" s="4" t="n">
-        <v>21.03</v>
+        <v>22.63</v>
       </c>
       <c r="X41" s="4" t="n">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="Y41" s="4" t="inlineStr">
         <is>
-          <t>R$ 81,01</t>
+          <t>R$ 80,14</t>
         </is>
       </c>
       <c r="Z41" s="4" t="inlineStr">
         <is>
-          <t>06:55</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="AA41" s="4" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="AB41" s="4" t="inlineStr">
@@ -6289,19 +6289,19 @@
         </is>
       </c>
       <c r="C21" s="27" t="n">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="D21" s="27" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E21" s="27" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="27" t="n">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>22.11</v>
+        <v>21.13</v>
       </c>
       <c r="H21" s="2" t="n"/>
       <c r="I21" s="2" t="n"/>
@@ -6869,19 +6869,19 @@
         </is>
       </c>
       <c r="C41" s="27" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="D41" s="27" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E41" s="27" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="27" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>25.71</v>
+        <v>23.4</v>
       </c>
       <c r="H41" s="2" t="n"/>
       <c r="I41" s="2" t="n"/>
@@ -6956,19 +6956,19 @@
         </is>
       </c>
       <c r="C44" s="41" t="n">
-        <v>7381</v>
+        <v>7425</v>
       </c>
       <c r="D44" s="41" t="n">
-        <v>2819</v>
+        <v>2823</v>
       </c>
       <c r="E44" s="41" t="n">
         <v>10</v>
       </c>
       <c r="F44" s="41" t="n">
-        <v>10210</v>
+        <v>10258</v>
       </c>
       <c r="G44" s="41" t="n">
-        <v>27.71</v>
+        <v>27.62</v>
       </c>
       <c r="H44" s="2" t="n"/>
       <c r="I44" s="2" t="n"/>
@@ -14845,7 +14845,7 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>08/09 a 10/09</t>
+          <t>08/09 a 11/09</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
@@ -14864,25 +14864,25 @@
         </is>
       </c>
       <c r="F65" s="5" t="n">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>6.16</v>
+        <v>6.59</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K65" s="5" t="n">
         <v>8</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>17.78</v>
+        <v>11.59</v>
       </c>
       <c r="M65" s="5" t="n">
         <v>0</v>
@@ -14891,7 +14891,7 @@
         <v>0</v>
       </c>
       <c r="O65" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P65" s="5" t="n">
         <v>0</v>
@@ -14910,27 +14910,27 @@
       <c r="V65" s="5" t="inlineStr"/>
       <c r="W65" s="5" t="inlineStr"/>
       <c r="X65" s="5" t="n">
-        <v>9.35</v>
+        <v>7.3</v>
       </c>
       <c r="Y65" s="5" t="n">
-        <v>18.7</v>
+        <v>21.9</v>
       </c>
       <c r="Z65" s="5" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="AA65" s="5" t="inlineStr">
         <is>
-          <t>R$ 95,76</t>
+          <t>R$ 87,45</t>
         </is>
       </c>
       <c r="AB65" s="5" t="inlineStr">
         <is>
-          <t>05:19</t>
+          <t>06:05</t>
         </is>
       </c>
       <c r="AC65" s="5" t="inlineStr">
         <is>
-          <t>06:47</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD65" s="5" t="inlineStr">
@@ -15685,7 +15685,7 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>09/09 a 09/09</t>
+          <t>09/09 a 11/09</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -15704,16 +15704,16 @@
         </is>
       </c>
       <c r="F73" s="4" t="n">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>39</v>
+        <v>29.5</v>
       </c>
       <c r="I73" s="4" t="n">
-        <v>4.9</v>
+        <v>5.12</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>5</v>
@@ -15722,7 +15722,7 @@
         <v>3</v>
       </c>
       <c r="L73" s="4" t="n">
-        <v>7.69</v>
+        <v>5.08</v>
       </c>
       <c r="M73" s="4" t="n">
         <v>0</v>
@@ -15731,7 +15731,7 @@
         <v>0</v>
       </c>
       <c r="O73" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P73" s="4" t="n">
         <v>0</v>
@@ -15750,37 +15750,37 @@
       <c r="V73" s="4" t="inlineStr"/>
       <c r="W73" s="4" t="inlineStr"/>
       <c r="X73" s="4" t="n">
-        <v>5.83</v>
+        <v>5.09</v>
       </c>
       <c r="Y73" s="4" t="n">
-        <v>5.83</v>
+        <v>10.18</v>
       </c>
       <c r="Z73" s="4" t="n">
-        <v>3.18</v>
+        <v>2.52</v>
       </c>
       <c r="AA73" s="4" t="inlineStr">
         <is>
-          <t>R$ 69,44</t>
+          <t>R$ 87,83</t>
         </is>
       </c>
       <c r="AB73" s="4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AC73" s="4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD73" s="4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AE73" s="4" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>15:39</t>
         </is>
       </c>
     </row>
@@ -16753,7 +16753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -17532,12 +17532,12 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Teonilda Florentino Vieira</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -17547,46 +17547,46 @@
         <v>21</v>
       </c>
       <c r="F25" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>76.90000000000001</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>🟡 BOM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G26" s="5" t="n">
         <v>75.3</v>
       </c>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
         <is>
           <t>🟡 BOM</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="36" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="36" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="C26" s="36" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E26" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="F26" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="G26" s="36" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="H26" s="36" t="inlineStr">
-        <is>
-          <t>🟠 ATENÇÃO</t>
         </is>
       </c>
     </row>
@@ -17596,7 +17596,7 @@
       </c>
       <c r="B27" s="36" t="inlineStr">
         <is>
-          <t>Adriano Ricardo Thiel</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="C27" s="36" t="inlineStr">
@@ -17611,10 +17611,10 @@
         <v>21</v>
       </c>
       <c r="F27" s="36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="36" t="n">
-        <v>72</v>
+        <v>74.2</v>
       </c>
       <c r="H27" s="36" t="inlineStr">
         <is>
@@ -17628,16 +17628,16 @@
       </c>
       <c r="B28" s="36" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Adriano Ricardo Thiel</t>
         </is>
       </c>
       <c r="C28" s="36" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="D28" s="36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="36" t="n">
         <v>21</v>
@@ -17660,25 +17660,25 @@
       </c>
       <c r="B29" s="36" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C29" s="36" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D29" s="36" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E29" s="36" t="n">
         <v>21</v>
       </c>
       <c r="F29" s="36" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G29" s="36" t="n">
-        <v>71.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="H29" s="36" t="inlineStr">
         <is>
@@ -17692,12 +17692,12 @@
       </c>
       <c r="B30" s="36" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C30" s="36" t="inlineStr">
         <is>
-          <t>Equipe 2</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D30" s="36" t="n">
@@ -17707,10 +17707,10 @@
         <v>21</v>
       </c>
       <c r="F30" s="36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G30" s="36" t="n">
-        <v>65.59999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="H30" s="36" t="inlineStr">
         <is>
@@ -17724,25 +17724,25 @@
       </c>
       <c r="B31" s="36" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C31" s="36" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 2</t>
         </is>
       </c>
       <c r="D31" s="36" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E31" s="36" t="n">
         <v>21</v>
       </c>
       <c r="F31" s="36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G31" s="36" t="n">
-        <v>64.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H31" s="36" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         </is>
       </c>
       <c r="D274" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E274" s="49" t="n">
         <v>1</v>
@@ -25471,7 +25471,7 @@
         <v>1</v>
       </c>
       <c r="H274" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275">
@@ -25619,7 +25619,7 @@
         </is>
       </c>
       <c r="D279" s="50" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E279" s="50" t="n">
         <v>1.5</v>
@@ -25631,7 +25631,7 @@
         <v>3</v>
       </c>
       <c r="H279" s="50" t="n">
-        <v>-21</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="280">
@@ -26291,7 +26291,7 @@
         </is>
       </c>
       <c r="D300" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E300" s="49" t="n">
         <v>1</v>
@@ -26303,7 +26303,7 @@
         <v>1</v>
       </c>
       <c r="H300" s="49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="301">
@@ -26351,11 +26351,11 @@
       </c>
       <c r="C302" s="50" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D302" s="50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E302" s="50" t="n">
         <v>0.3</v>
@@ -26367,7 +26367,7 @@
         <v>0.6</v>
       </c>
       <c r="H302" s="50" t="n">
-        <v>-2.4</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="303">
@@ -26383,11 +26383,11 @@
       </c>
       <c r="C303" s="50" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D303" s="50" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E303" s="50" t="n">
         <v>0.3</v>
@@ -26399,7 +26399,7 @@
         <v>0.6</v>
       </c>
       <c r="H303" s="50" t="n">
-        <v>-0.6</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="304">
@@ -26415,23 +26415,23 @@
       </c>
       <c r="C304" s="50" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D304" s="50" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E304" s="50" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F304" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G304" s="50" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H304" s="50" t="n">
-        <v>-27</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="305">
@@ -26447,87 +26447,87 @@
       </c>
       <c r="C305" s="50" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D305" s="50" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E305" s="50" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F305" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G305" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H305" s="50" t="n">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="50" t="inlineStr">
+        <is>
+          <t>Teonilda Florentino Vieira</t>
+        </is>
+      </c>
+      <c r="B306" s="50" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C306" s="50" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D306" s="50" t="n">
+        <v>6</v>
+      </c>
+      <c r="E306" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F306" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G306" s="50" t="n">
         <v>0.4</v>
       </c>
-      <c r="H305" s="50" t="n">
+      <c r="H306" s="50" t="n">
         <v>-2.4</v>
       </c>
     </row>
-    <row r="306">
-      <c r="A306" s="49" t="inlineStr">
+    <row r="307">
+      <c r="A307" s="49" t="inlineStr">
         <is>
           <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
-      <c r="B306" s="49" t="inlineStr">
+      <c r="B307" s="49" t="inlineStr">
         <is>
           <t>Equipe 1</t>
         </is>
       </c>
-      <c r="C306" s="49" t="inlineStr">
+      <c r="C307" s="49" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D306" s="49" t="n">
+      <c r="D307" s="49" t="n">
         <v>5</v>
       </c>
-      <c r="E306" s="49" t="n">
+      <c r="E307" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F306" s="49" t="n">
+      <c r="F307" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G306" s="49" t="n">
+      <c r="G307" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H306" s="49" t="n">
+      <c r="H307" s="49" t="n">
         <v>5</v>
-      </c>
-    </row>
-    <row r="307">
-      <c r="A307" s="50" t="inlineStr">
-        <is>
-          <t>Wagner Tarlei Gomes</t>
-        </is>
-      </c>
-      <c r="B307" s="50" t="inlineStr">
-        <is>
-          <t>Equipe 1</t>
-        </is>
-      </c>
-      <c r="C307" s="50" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D307" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="E307" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F307" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G307" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H307" s="50" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="308">
@@ -26543,23 +26543,23 @@
       </c>
       <c r="C308" s="50" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D308" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="E308" s="50" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F308" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="E308" s="50" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F308" s="50" t="n">
-        <v>2</v>
-      </c>
       <c r="G308" s="50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H308" s="50" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="309">
@@ -26575,11 +26575,11 @@
       </c>
       <c r="C309" s="50" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D309" s="50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E309" s="50" t="n">
         <v>0.3</v>
@@ -26591,7 +26591,7 @@
         <v>0.6</v>
       </c>
       <c r="H309" s="50" t="n">
-        <v>-1.8</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="310">
@@ -26607,11 +26607,11 @@
       </c>
       <c r="C310" s="50" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D310" s="50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E310" s="50" t="n">
         <v>0.3</v>
@@ -26623,7 +26623,7 @@
         <v>0.6</v>
       </c>
       <c r="H310" s="50" t="n">
-        <v>-2.4</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="311">
@@ -26639,11 +26639,11 @@
       </c>
       <c r="C311" s="50" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D311" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E311" s="50" t="n">
         <v>0.3</v>
@@ -26655,7 +26655,7 @@
         <v>0.6</v>
       </c>
       <c r="H311" s="50" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="312">
@@ -26671,23 +26671,23 @@
       </c>
       <c r="C312" s="50" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D312" s="50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E312" s="50" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F312" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G312" s="50" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H312" s="50" t="n">
-        <v>-15</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="313">
@@ -26703,87 +26703,87 @@
       </c>
       <c r="C313" s="50" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D313" s="50" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E313" s="50" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F313" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G313" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H313" s="50" t="n">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="50" t="inlineStr">
+        <is>
+          <t>Wagner Tarlei Gomes</t>
+        </is>
+      </c>
+      <c r="B314" s="50" t="inlineStr">
+        <is>
+          <t>Equipe 1</t>
+        </is>
+      </c>
+      <c r="C314" s="50" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D314" s="50" t="n">
+        <v>22</v>
+      </c>
+      <c r="E314" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F314" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G314" s="50" t="n">
         <v>0.4</v>
       </c>
-      <c r="H313" s="50" t="n">
+      <c r="H314" s="50" t="n">
         <v>-8.800000000000001</v>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="49" t="inlineStr">
+    <row r="315">
+      <c r="A315" s="49" t="inlineStr">
         <is>
           <t>Walquiria Araujo Flores</t>
         </is>
       </c>
-      <c r="B314" s="49" t="inlineStr">
+      <c r="B315" s="49" t="inlineStr">
         <is>
           <t>Equipe 4</t>
         </is>
       </c>
-      <c r="C314" s="49" t="inlineStr">
+      <c r="C315" s="49" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D314" s="49" t="n">
+      <c r="D315" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="E314" s="49" t="n">
+      <c r="E315" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F314" s="49" t="n">
+      <c r="F315" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G314" s="49" t="n">
+      <c r="G315" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H314" s="49" t="n">
+      <c r="H315" s="49" t="n">
         <v>4</v>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" s="50" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="B315" s="50" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="C315" s="50" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D315" s="50" t="n">
-        <v>4</v>
-      </c>
-      <c r="E315" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F315" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G315" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H315" s="50" t="n">
-        <v>-2</v>
       </c>
     </row>
     <row r="316">
@@ -26799,23 +26799,23 @@
       </c>
       <c r="C316" s="50" t="inlineStr">
         <is>
-          <t>Fim manhã antes de 10h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D316" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E316" s="50" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F316" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G316" s="50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H316" s="50" t="n">
-        <v>-1.2</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="317">
@@ -26831,11 +26831,11 @@
       </c>
       <c r="C317" s="50" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Fim manhã antes de 10h00</t>
         </is>
       </c>
       <c r="D317" s="50" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E317" s="50" t="n">
         <v>0.3</v>
@@ -26847,7 +26847,7 @@
         <v>0.6</v>
       </c>
       <c r="H317" s="50" t="n">
-        <v>-2.4</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="318">
@@ -26863,7 +26863,7 @@
       </c>
       <c r="C318" s="50" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D318" s="50" t="n">
@@ -26895,11 +26895,11 @@
       </c>
       <c r="C319" s="50" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D319" s="50" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E319" s="50" t="n">
         <v>0.3</v>
@@ -26911,7 +26911,7 @@
         <v>0.6</v>
       </c>
       <c r="H319" s="50" t="n">
-        <v>-1.2</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="320">
@@ -26927,23 +26927,23 @@
       </c>
       <c r="C320" s="50" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D320" s="50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E320" s="50" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F320" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G320" s="50" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H320" s="50" t="n">
-        <v>-18</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="321">
@@ -26959,87 +26959,87 @@
       </c>
       <c r="C321" s="50" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D321" s="50" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E321" s="50" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F321" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G321" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H321" s="50" t="n">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="50" t="inlineStr">
+        <is>
+          <t>Walquiria Araujo Flores</t>
+        </is>
+      </c>
+      <c r="B322" s="50" t="inlineStr">
+        <is>
+          <t>Equipe 4</t>
+        </is>
+      </c>
+      <c r="C322" s="50" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D322" s="50" t="n">
+        <v>12</v>
+      </c>
+      <c r="E322" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F322" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G322" s="50" t="n">
         <v>0.4</v>
       </c>
-      <c r="H321" s="50" t="n">
+      <c r="H322" s="50" t="n">
         <v>-4.8</v>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" s="49" t="inlineStr">
+    <row r="323">
+      <c r="A323" s="49" t="inlineStr">
         <is>
           <t>Wesley de Souza Leal</t>
         </is>
       </c>
-      <c r="B322" s="49" t="inlineStr">
+      <c r="B323" s="49" t="inlineStr">
         <is>
           <t>Equipe 2</t>
         </is>
       </c>
-      <c r="C322" s="49" t="inlineStr">
+      <c r="C323" s="49" t="inlineStr">
         <is>
           <t>Dia com meta diária batida</t>
         </is>
       </c>
-      <c r="D322" s="49" t="n">
+      <c r="D323" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="E322" s="49" t="n">
+      <c r="E323" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="F322" s="49" t="n">
+      <c r="F323" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="G322" s="49" t="n">
+      <c r="G323" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H322" s="49" t="n">
+      <c r="H323" s="49" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" s="50" t="inlineStr">
-        <is>
-          <t>Wesley de Souza Leal</t>
-        </is>
-      </c>
-      <c r="B323" s="50" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C323" s="50" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D323" s="50" t="n">
-        <v>3</v>
-      </c>
-      <c r="E323" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F323" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G323" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H323" s="50" t="n">
-        <v>-1.5</v>
       </c>
     </row>
     <row r="324">
@@ -27055,23 +27055,23 @@
       </c>
       <c r="C324" s="50" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D324" s="50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E324" s="50" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F324" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G324" s="50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H324" s="50" t="n">
-        <v>-1.2</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="325">
@@ -27087,11 +27087,11 @@
       </c>
       <c r="C325" s="50" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D325" s="50" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E325" s="50" t="n">
         <v>0.3</v>
@@ -27103,7 +27103,7 @@
         <v>0.6</v>
       </c>
       <c r="H325" s="50" t="n">
-        <v>-3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="326">
@@ -27119,11 +27119,11 @@
       </c>
       <c r="C326" s="50" t="inlineStr">
         <is>
-          <t>Início tarde após 14h30</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D326" s="50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E326" s="50" t="n">
         <v>0.3</v>
@@ -27135,7 +27135,7 @@
         <v>0.6</v>
       </c>
       <c r="H326" s="50" t="n">
-        <v>-2.4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="327">
@@ -27151,23 +27151,23 @@
       </c>
       <c r="C327" s="50" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início tarde após 14h30</t>
         </is>
       </c>
       <c r="D327" s="50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E327" s="50" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F327" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G327" s="50" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="H327" s="50" t="n">
-        <v>-9</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="328">
@@ -27183,55 +27183,55 @@
       </c>
       <c r="C328" s="50" t="inlineStr">
         <is>
-          <t>Visita rápida</t>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
         </is>
       </c>
       <c r="D328" s="50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E328" s="50" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
       </c>
       <c r="F328" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G328" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H328" s="50" t="n">
+        <v>-9</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="50" t="inlineStr">
+        <is>
+          <t>Wesley de Souza Leal</t>
+        </is>
+      </c>
+      <c r="B329" s="50" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C329" s="50" t="inlineStr">
+        <is>
+          <t>Visita rápida</t>
+        </is>
+      </c>
+      <c r="D329" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E329" s="50" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F329" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G329" s="50" t="n">
         <v>0.4</v>
       </c>
-      <c r="H328" s="50" t="n">
+      <c r="H329" s="50" t="n">
         <v>-0.4</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="49" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B329" s="49" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C329" s="49" t="inlineStr">
-        <is>
-          <t>Bônus: nenhuma visita rápida no período</t>
-        </is>
-      </c>
-      <c r="D329" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E329" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="F329" s="49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G329" s="49" t="n">
-        <v>5</v>
-      </c>
-      <c r="H329" s="49" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="330">
@@ -27247,55 +27247,55 @@
       </c>
       <c r="C330" s="49" t="inlineStr">
         <is>
-          <t>Dia com meta diária batida</t>
+          <t>Bônus: nenhuma visita rápida no período</t>
         </is>
       </c>
       <c r="D330" s="49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E330" s="49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F330" s="49" t="n">
         <v>1</v>
       </c>
       <c r="G330" s="49" t="n">
+        <v>5</v>
+      </c>
+      <c r="H330" s="49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="49" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B331" s="49" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C331" s="49" t="inlineStr">
+        <is>
+          <t>Dia com meta diária batida</t>
+        </is>
+      </c>
+      <c r="D331" s="49" t="n">
+        <v>7</v>
+      </c>
+      <c r="E331" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="H330" s="49" t="n">
+      <c r="F331" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="G331" s="49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" s="49" t="n">
         <v>7</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" s="50" t="inlineStr">
-        <is>
-          <t>William Anderson Chamorro Tavares</t>
-        </is>
-      </c>
-      <c r="B331" s="50" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="C331" s="50" t="inlineStr">
-        <is>
-          <t>Dia sem bater a meta diária</t>
-        </is>
-      </c>
-      <c r="D331" s="50" t="n">
-        <v>2</v>
-      </c>
-      <c r="E331" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F331" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G331" s="50" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H331" s="50" t="n">
-        <v>-1</v>
       </c>
     </row>
     <row r="332">
@@ -27311,23 +27311,23 @@
       </c>
       <c r="C332" s="50" t="inlineStr">
         <is>
-          <t>Fim tarde antes de 16h00</t>
+          <t>Dia sem bater a meta diária</t>
         </is>
       </c>
       <c r="D332" s="50" t="n">
         <v>2</v>
       </c>
       <c r="E332" s="50" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F332" s="50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G332" s="50" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="H332" s="50" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="333">
@@ -27343,11 +27343,11 @@
       </c>
       <c r="C333" s="50" t="inlineStr">
         <is>
-          <t>Início manhã após 08h30</t>
+          <t>Fim tarde antes de 16h00</t>
         </is>
       </c>
       <c r="D333" s="50" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E333" s="50" t="n">
         <v>0.3</v>
@@ -27359,7 +27359,7 @@
         <v>0.6</v>
       </c>
       <c r="H333" s="50" t="n">
-        <v>-3.6</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="334">
@@ -27375,22 +27375,54 @@
       </c>
       <c r="C334" s="50" t="inlineStr">
         <is>
-          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+          <t>Início manhã após 08h30</t>
         </is>
       </c>
       <c r="D334" s="50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E334" s="50" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="F334" s="50" t="n">
         <v>2</v>
       </c>
       <c r="G334" s="50" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H334" s="50" t="n">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="50" t="inlineStr">
+        <is>
+          <t>William Anderson Chamorro Tavares</t>
+        </is>
+      </c>
+      <c r="B335" s="50" t="inlineStr">
+        <is>
+          <t>Equipe 2</t>
+        </is>
+      </c>
+      <c r="C335" s="50" t="inlineStr">
+        <is>
+          <t>Turno sem lançamento (não é chuva/reunião/férias)</t>
+        </is>
+      </c>
+      <c r="D335" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="H334" s="50" t="n">
+      <c r="E335" s="50" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F335" s="50" t="n">
+        <v>2</v>
+      </c>
+      <c r="G335" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="H335" s="50" t="n">
         <v>-9</v>
       </c>
     </row>
@@ -28510,10 +28542,10 @@
         </is>
       </c>
       <c r="D21" s="4" t="n">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>5.06</v>
+        <v>5.12</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>5</v>
@@ -28530,16 +28562,16 @@
         <v>6</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4.05</v>
+        <v>3.57</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>22.11</v>
+        <v>21.13</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -29914,36 +29946,36 @@
         </is>
       </c>
       <c r="D47" s="4" t="n">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="E47" s="4" t="n">
-        <v>7.35</v>
+        <v>7.36</v>
       </c>
       <c r="F47" s="4" t="n">
         <v>7</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Q001, Q002, Q003, Q004, Q005, Q006, Q008, Q009, Q018, Q019, Q024</t>
+          <t>Q001, Q002, Q003, Q004, Q005, Q006, Q008, Q009, Q018, Q019, Q022, Q023, Q024, Q025, Q026</t>
         </is>
       </c>
       <c r="I47" s="4" t="n">
         <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>7.05</v>
+        <v>6.11</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L47" s="4" t="n">
         <v>1</v>
       </c>
       <c r="M47" s="4" t="n">
-        <v>25.71</v>
+        <v>23.4</v>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
@@ -31130,7 +31162,7 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>17349010</t>
+          <t>17349009</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -31150,7 +31182,7 @@
       </c>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t>04 - TB</t>
+          <t>03 - OU</t>
         </is>
       </c>
       <c r="I15" s="23" t="inlineStr">
@@ -31160,7 +31192,7 @@
       </c>
       <c r="J15" s="23" t="inlineStr">
         <is>
-          <t>08/09/2026 16:00</t>
+          <t>08/09/2026 15:56</t>
         </is>
       </c>
       <c r="K15" s="23" t="inlineStr"/>
@@ -31181,7 +31213,7 @@
       </c>
       <c r="D16" s="24" t="inlineStr">
         <is>
-          <t>17349009</t>
+          <t>17349010</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -31201,7 +31233,7 @@
       </c>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t>03 - OU</t>
+          <t>04 - TB</t>
         </is>
       </c>
       <c r="I16" s="23" t="inlineStr">
@@ -31211,7 +31243,7 @@
       </c>
       <c r="J16" s="23" t="inlineStr">
         <is>
-          <t>08/09/2026 15:56</t>
+          <t>08/09/2026 16:00</t>
         </is>
       </c>
       <c r="K16" s="23" t="n">
@@ -35609,7 +35641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -35624,7 +35656,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (182 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
+          <t>POSSÍVEIS AUSÊNCIAS POR DIA/TURNO (179 registros) — CONFIRMAR COM A ESCALA (FOLGA/ATESTADO/FALTA)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -38193,11 +38225,11 @@
     </row>
     <row r="75">
       <c r="A75" s="37" t="n">
-        <v>3035</v>
+        <v>2030</v>
       </c>
       <c r="B75" s="37" t="inlineStr">
         <is>
-          <t>Teonilda Florentino Vieira</t>
+          <t>Mateus Falcao de Souza</t>
         </is>
       </c>
       <c r="C75" s="37" t="inlineStr">
@@ -38217,7 +38249,7 @@
       </c>
       <c r="F75" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G75" s="37" t="inlineStr">
@@ -38228,11 +38260,11 @@
     </row>
     <row r="76">
       <c r="A76" s="37" t="n">
-        <v>2030</v>
+        <v>3127</v>
       </c>
       <c r="B76" s="37" t="inlineStr">
         <is>
-          <t>Mateus Falcao de Souza</t>
+          <t>Gisele Olimpia Torres</t>
         </is>
       </c>
       <c r="C76" s="37" t="inlineStr">
@@ -38242,17 +38274,17 @@
       </c>
       <c r="D76" s="37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E76" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F76" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G76" s="37" t="inlineStr">
@@ -38262,82 +38294,82 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="37" t="n">
-        <v>3035</v>
-      </c>
-      <c r="B77" s="37" t="inlineStr">
-        <is>
-          <t>Teonilda Florentino Vieira</t>
-        </is>
-      </c>
-      <c r="C77" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D77" s="37" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E77" s="37" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F77" s="37" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G77" s="37" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+      <c r="A77" s="36" t="n">
+        <v>2951</v>
+      </c>
+      <c r="B77" s="36" t="inlineStr">
+        <is>
+          <t>Alana Amanda Fernandes Ovelar</t>
+        </is>
+      </c>
+      <c r="C77" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D77" s="36" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E77" s="36" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F77" s="36" t="inlineStr">
+        <is>
+          <t>Manhã</t>
+        </is>
+      </c>
+      <c r="G77" s="36" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="37" t="n">
-        <v>3127</v>
-      </c>
-      <c r="B78" s="37" t="inlineStr">
-        <is>
-          <t>Gisele Olimpia Torres</t>
-        </is>
-      </c>
-      <c r="C78" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 2</t>
-        </is>
-      </c>
-      <c r="D78" s="37" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E78" s="37" t="inlineStr">
-        <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="F78" s="37" t="inlineStr">
+      <c r="A78" s="36" t="n">
+        <v>2918</v>
+      </c>
+      <c r="B78" s="36" t="inlineStr">
+        <is>
+          <t>Claine Luisa Figueiredo Torraca</t>
+        </is>
+      </c>
+      <c r="C78" s="36" t="inlineStr">
+        <is>
+          <t>Equipe 3</t>
+        </is>
+      </c>
+      <c r="D78" s="36" t="inlineStr">
+        <is>
+          <t>01/09/2026</t>
+        </is>
+      </c>
+      <c r="E78" s="36" t="inlineStr">
+        <is>
+          <t>Terça</t>
+        </is>
+      </c>
+      <c r="F78" s="36" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G78" s="37" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
+      <c r="G78" s="36" t="inlineStr">
+        <is>
+          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="36" t="n">
-        <v>2951</v>
+        <v>120</v>
       </c>
       <c r="B79" s="36" t="inlineStr">
         <is>
-          <t>Alana Amanda Fernandes Ovelar</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C79" s="36" t="inlineStr">
@@ -38368,11 +38400,11 @@
     </row>
     <row r="80">
       <c r="A80" s="36" t="n">
-        <v>2918</v>
+        <v>1936</v>
       </c>
       <c r="B80" s="36" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C80" s="36" t="inlineStr">
@@ -38403,11 +38435,11 @@
     </row>
     <row r="81">
       <c r="A81" s="36" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B81" s="36" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C81" s="36" t="inlineStr">
@@ -38438,11 +38470,11 @@
     </row>
     <row r="82">
       <c r="A82" s="36" t="n">
-        <v>1936</v>
+        <v>2721</v>
       </c>
       <c r="B82" s="36" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C82" s="36" t="inlineStr">
@@ -38473,11 +38505,11 @@
     </row>
     <row r="83">
       <c r="A83" s="36" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B83" s="36" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C83" s="36" t="inlineStr">
@@ -38508,11 +38540,11 @@
     </row>
     <row r="84">
       <c r="A84" s="36" t="n">
-        <v>2721</v>
+        <v>3128</v>
       </c>
       <c r="B84" s="36" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C84" s="36" t="inlineStr">
@@ -38543,11 +38575,11 @@
     </row>
     <row r="85">
       <c r="A85" s="36" t="n">
-        <v>3038</v>
+        <v>113</v>
       </c>
       <c r="B85" s="36" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C85" s="36" t="inlineStr">
@@ -38577,72 +38609,72 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="36" t="n">
-        <v>3128</v>
-      </c>
-      <c r="B86" s="36" t="inlineStr">
-        <is>
-          <t>Rosalina Beniel Vargas</t>
-        </is>
-      </c>
-      <c r="C86" s="36" t="inlineStr">
+      <c r="A86" s="37" t="n">
+        <v>1938</v>
+      </c>
+      <c r="B86" s="37" t="inlineStr">
+        <is>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
+        </is>
+      </c>
+      <c r="C86" s="37" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D86" s="36" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
-      <c r="E86" s="36" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F86" s="36" t="inlineStr">
+      <c r="D86" s="37" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="E86" s="37" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F86" s="37" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G86" s="36" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G86" s="37" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="36" t="n">
+      <c r="A87" s="37" t="n">
         <v>113</v>
       </c>
-      <c r="B87" s="36" t="inlineStr">
+      <c r="B87" s="37" t="inlineStr">
         <is>
           <t>Selba Ramona Afonso</t>
         </is>
       </c>
-      <c r="C87" s="36" t="inlineStr">
+      <c r="C87" s="37" t="inlineStr">
         <is>
           <t>Equipe 3</t>
         </is>
       </c>
-      <c r="D87" s="36" t="inlineStr">
-        <is>
-          <t>01/09/2026</t>
-        </is>
-      </c>
-      <c r="E87" s="36" t="inlineStr">
-        <is>
-          <t>Terça</t>
-        </is>
-      </c>
-      <c r="F87" s="36" t="inlineStr">
+      <c r="D87" s="37" t="inlineStr">
+        <is>
+          <t>02/09/2026</t>
+        </is>
+      </c>
+      <c r="E87" s="37" t="inlineStr">
+        <is>
+          <t>Quarta</t>
+        </is>
+      </c>
+      <c r="F87" s="37" t="inlineStr">
         <is>
           <t>Manhã</t>
         </is>
       </c>
-      <c r="G87" s="36" t="inlineStr">
-        <is>
-          <t>TODA A EQUIPE (9 agentes) ausente nesse turno — possível reunião de equipe, chuva/intempérie ou evento — verificar</t>
+      <c r="G87" s="37" t="inlineStr">
+        <is>
+          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
         </is>
       </c>
     </row>
@@ -38672,7 +38704,7 @@
       </c>
       <c r="F88" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G88" s="37" t="inlineStr">
@@ -38707,7 +38739,7 @@
       </c>
       <c r="F89" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G89" s="37" t="inlineStr">
@@ -38732,17 +38764,17 @@
       </c>
       <c r="D90" s="37" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E90" s="37" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F90" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G90" s="37" t="inlineStr">
@@ -38753,11 +38785,11 @@
     </row>
     <row r="91">
       <c r="A91" s="37" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B91" s="37" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C91" s="37" t="inlineStr">
@@ -38767,12 +38799,12 @@
       </c>
       <c r="D91" s="37" t="inlineStr">
         <is>
-          <t>02/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E91" s="37" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F91" s="37" t="inlineStr">
@@ -38788,11 +38820,11 @@
     </row>
     <row r="92">
       <c r="A92" s="37" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B92" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C92" s="37" t="inlineStr">
@@ -38802,12 +38834,12 @@
       </c>
       <c r="D92" s="37" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E92" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F92" s="37" t="inlineStr">
@@ -38837,17 +38869,17 @@
       </c>
       <c r="D93" s="37" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E93" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F93" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G93" s="37" t="inlineStr">
@@ -38858,11 +38890,11 @@
     </row>
     <row r="94">
       <c r="A94" s="37" t="n">
-        <v>2918</v>
+        <v>1936</v>
       </c>
       <c r="B94" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C94" s="37" t="inlineStr">
@@ -38893,11 +38925,11 @@
     </row>
     <row r="95">
       <c r="A95" s="37" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B95" s="37" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C95" s="37" t="inlineStr">
@@ -38928,11 +38960,11 @@
     </row>
     <row r="96">
       <c r="A96" s="37" t="n">
-        <v>1936</v>
+        <v>2721</v>
       </c>
       <c r="B96" s="37" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C96" s="37" t="inlineStr">
@@ -38963,11 +38995,11 @@
     </row>
     <row r="97">
       <c r="A97" s="37" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B97" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C97" s="37" t="inlineStr">
@@ -38998,11 +39030,11 @@
     </row>
     <row r="98">
       <c r="A98" s="37" t="n">
-        <v>2721</v>
+        <v>3128</v>
       </c>
       <c r="B98" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C98" s="37" t="inlineStr">
@@ -39033,11 +39065,11 @@
     </row>
     <row r="99">
       <c r="A99" s="37" t="n">
-        <v>3038</v>
+        <v>113</v>
       </c>
       <c r="B99" s="37" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C99" s="37" t="inlineStr">
@@ -39068,11 +39100,11 @@
     </row>
     <row r="100">
       <c r="A100" s="37" t="n">
-        <v>3128</v>
+        <v>120</v>
       </c>
       <c r="B100" s="37" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C100" s="37" t="inlineStr">
@@ -39092,7 +39124,7 @@
       </c>
       <c r="F100" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G100" s="37" t="inlineStr">
@@ -39103,11 +39135,11 @@
     </row>
     <row r="101">
       <c r="A101" s="37" t="n">
-        <v>113</v>
+        <v>2721</v>
       </c>
       <c r="B101" s="37" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C101" s="37" t="inlineStr">
@@ -39127,7 +39159,7 @@
       </c>
       <c r="F101" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G101" s="37" t="inlineStr">
@@ -39138,11 +39170,11 @@
     </row>
     <row r="102">
       <c r="A102" s="37" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B102" s="37" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Selba Ramona Afonso</t>
         </is>
       </c>
       <c r="C102" s="37" t="inlineStr">
@@ -39173,11 +39205,11 @@
     </row>
     <row r="103">
       <c r="A103" s="37" t="n">
-        <v>2721</v>
+        <v>2918</v>
       </c>
       <c r="B103" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C103" s="37" t="inlineStr">
@@ -39187,17 +39219,17 @@
       </c>
       <c r="D103" s="37" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E103" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F103" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G103" s="37" t="inlineStr">
@@ -39208,11 +39240,11 @@
     </row>
     <row r="104">
       <c r="A104" s="37" t="n">
-        <v>113</v>
+        <v>1938</v>
       </c>
       <c r="B104" s="37" t="inlineStr">
         <is>
-          <t>Selba Ramona Afonso</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C104" s="37" t="inlineStr">
@@ -39222,17 +39254,17 @@
       </c>
       <c r="D104" s="37" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E104" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F104" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G104" s="37" t="inlineStr">
@@ -39243,11 +39275,11 @@
     </row>
     <row r="105">
       <c r="A105" s="37" t="n">
-        <v>2918</v>
+        <v>2721</v>
       </c>
       <c r="B105" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C105" s="37" t="inlineStr">
@@ -39278,11 +39310,11 @@
     </row>
     <row r="106">
       <c r="A106" s="37" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B106" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C106" s="37" t="inlineStr">
@@ -39302,7 +39334,7 @@
       </c>
       <c r="F106" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G106" s="37" t="inlineStr">
@@ -39337,7 +39369,7 @@
       </c>
       <c r="F107" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G107" s="37" t="inlineStr">
@@ -39348,11 +39380,11 @@
     </row>
     <row r="108">
       <c r="A108" s="37" t="n">
-        <v>2918</v>
+        <v>1938</v>
       </c>
       <c r="B108" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C108" s="37" t="inlineStr">
@@ -39362,17 +39394,17 @@
       </c>
       <c r="D108" s="37" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E108" s="37" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F108" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G108" s="37" t="inlineStr">
@@ -39397,17 +39429,17 @@
       </c>
       <c r="D109" s="37" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E109" s="37" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F109" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G109" s="37" t="inlineStr">
@@ -39442,7 +39474,7 @@
       </c>
       <c r="F110" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G110" s="37" t="inlineStr">
@@ -39477,7 +39509,7 @@
       </c>
       <c r="F111" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G111" s="37" t="inlineStr">
@@ -39488,11 +39520,11 @@
     </row>
     <row r="112">
       <c r="A112" s="37" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B112" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C112" s="37" t="inlineStr">
@@ -39523,11 +39555,11 @@
     </row>
     <row r="113">
       <c r="A113" s="37" t="n">
-        <v>2721</v>
+        <v>2918</v>
       </c>
       <c r="B113" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C113" s="37" t="inlineStr">
@@ -39537,17 +39569,17 @@
       </c>
       <c r="D113" s="37" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E113" s="37" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F113" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G113" s="37" t="inlineStr">
@@ -39558,11 +39590,11 @@
     </row>
     <row r="114">
       <c r="A114" s="37" t="n">
-        <v>3038</v>
+        <v>120</v>
       </c>
       <c r="B114" s="37" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C114" s="37" t="inlineStr">
@@ -39572,17 +39604,17 @@
       </c>
       <c r="D114" s="37" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E114" s="37" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F114" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G114" s="37" t="inlineStr">
@@ -39593,11 +39625,11 @@
     </row>
     <row r="115">
       <c r="A115" s="37" t="n">
-        <v>2918</v>
+        <v>1936</v>
       </c>
       <c r="B115" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Geancarlos Ferreira Barrios</t>
         </is>
       </c>
       <c r="C115" s="37" t="inlineStr">
@@ -39628,11 +39660,11 @@
     </row>
     <row r="116">
       <c r="A116" s="37" t="n">
-        <v>120</v>
+        <v>1938</v>
       </c>
       <c r="B116" s="37" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C116" s="37" t="inlineStr">
@@ -39663,11 +39695,11 @@
     </row>
     <row r="117">
       <c r="A117" s="37" t="n">
-        <v>1936</v>
+        <v>2721</v>
       </c>
       <c r="B117" s="37" t="inlineStr">
         <is>
-          <t>Geancarlos Ferreira Barrios</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C117" s="37" t="inlineStr">
@@ -39698,11 +39730,11 @@
     </row>
     <row r="118">
       <c r="A118" s="37" t="n">
-        <v>1938</v>
+        <v>3038</v>
       </c>
       <c r="B118" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Naime Cristina Freitas</t>
         </is>
       </c>
       <c r="C118" s="37" t="inlineStr">
@@ -39733,11 +39765,11 @@
     </row>
     <row r="119">
       <c r="A119" s="37" t="n">
-        <v>2721</v>
+        <v>3128</v>
       </c>
       <c r="B119" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Rosalina Beniel Vargas</t>
         </is>
       </c>
       <c r="C119" s="37" t="inlineStr">
@@ -39768,11 +39800,11 @@
     </row>
     <row r="120">
       <c r="A120" s="37" t="n">
-        <v>3038</v>
+        <v>2918</v>
       </c>
       <c r="B120" s="37" t="inlineStr">
         <is>
-          <t>Naime Cristina Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C120" s="37" t="inlineStr">
@@ -39792,7 +39824,7 @@
       </c>
       <c r="F120" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G120" s="37" t="inlineStr">
@@ -39803,11 +39835,11 @@
     </row>
     <row r="121">
       <c r="A121" s="37" t="n">
-        <v>3128</v>
+        <v>120</v>
       </c>
       <c r="B121" s="37" t="inlineStr">
         <is>
-          <t>Rosalina Beniel Vargas</t>
+          <t>Emidio Rainer Vilhalba</t>
         </is>
       </c>
       <c r="C121" s="37" t="inlineStr">
@@ -39827,7 +39859,7 @@
       </c>
       <c r="F121" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G121" s="37" t="inlineStr">
@@ -39838,11 +39870,11 @@
     </row>
     <row r="122">
       <c r="A122" s="37" t="n">
-        <v>2918</v>
+        <v>1938</v>
       </c>
       <c r="B122" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C122" s="37" t="inlineStr">
@@ -39873,11 +39905,11 @@
     </row>
     <row r="123">
       <c r="A123" s="37" t="n">
-        <v>120</v>
+        <v>2721</v>
       </c>
       <c r="B123" s="37" t="inlineStr">
         <is>
-          <t>Emidio Rainer Vilhalba</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C123" s="37" t="inlineStr">
@@ -39908,11 +39940,11 @@
     </row>
     <row r="124">
       <c r="A124" s="37" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B124" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C124" s="37" t="inlineStr">
@@ -39922,17 +39954,17 @@
       </c>
       <c r="D124" s="37" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E124" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F124" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G124" s="37" t="inlineStr">
@@ -39943,11 +39975,11 @@
     </row>
     <row r="125">
       <c r="A125" s="37" t="n">
-        <v>2721</v>
+        <v>1938</v>
       </c>
       <c r="B125" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C125" s="37" t="inlineStr">
@@ -39957,17 +39989,17 @@
       </c>
       <c r="D125" s="37" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E125" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F125" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G125" s="37" t="inlineStr">
@@ -39978,11 +40010,11 @@
     </row>
     <row r="126">
       <c r="A126" s="37" t="n">
-        <v>2918</v>
+        <v>2721</v>
       </c>
       <c r="B126" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C126" s="37" t="inlineStr">
@@ -40013,11 +40045,11 @@
     </row>
     <row r="127">
       <c r="A127" s="37" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B127" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C127" s="37" t="inlineStr">
@@ -40037,7 +40069,7 @@
       </c>
       <c r="F127" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G127" s="37" t="inlineStr">
@@ -40048,11 +40080,11 @@
     </row>
     <row r="128">
       <c r="A128" s="37" t="n">
-        <v>2721</v>
+        <v>1938</v>
       </c>
       <c r="B128" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Marco Antonio Ayala de Matos Freitas</t>
         </is>
       </c>
       <c r="C128" s="37" t="inlineStr">
@@ -40072,7 +40104,7 @@
       </c>
       <c r="F128" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G128" s="37" t="inlineStr">
@@ -40083,11 +40115,11 @@
     </row>
     <row r="129">
       <c r="A129" s="37" t="n">
-        <v>2918</v>
+        <v>2721</v>
       </c>
       <c r="B129" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="C129" s="37" t="inlineStr">
@@ -40132,17 +40164,17 @@
       </c>
       <c r="D130" s="37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E130" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F130" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G130" s="37" t="inlineStr">
@@ -40167,17 +40199,17 @@
       </c>
       <c r="D131" s="37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E131" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F131" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G131" s="37" t="inlineStr">
@@ -40188,11 +40220,11 @@
     </row>
     <row r="132">
       <c r="A132" s="37" t="n">
-        <v>1938</v>
+        <v>2918</v>
       </c>
       <c r="B132" s="37" t="inlineStr">
         <is>
-          <t>Marco Antonio Ayala de Matos Freitas</t>
+          <t>Claine Luisa Figueiredo Torraca</t>
         </is>
       </c>
       <c r="C132" s="37" t="inlineStr">
@@ -40212,7 +40244,7 @@
       </c>
       <c r="F132" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G132" s="37" t="inlineStr">
@@ -40223,26 +40255,26 @@
     </row>
     <row r="133">
       <c r="A133" s="37" t="n">
-        <v>2721</v>
+        <v>80</v>
       </c>
       <c r="B133" s="37" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C133" s="37" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D133" s="37" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E133" s="37" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F133" s="37" t="inlineStr">
@@ -40258,31 +40290,31 @@
     </row>
     <row r="134">
       <c r="A134" s="37" t="n">
-        <v>2918</v>
+        <v>2789</v>
       </c>
       <c r="B134" s="37" t="inlineStr">
         <is>
-          <t>Claine Luisa Figueiredo Torraca</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C134" s="37" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="D134" s="37" t="inlineStr">
         <is>
-          <t>31/08/2026</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="E134" s="37" t="inlineStr">
         <is>
-          <t>Segunda</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F134" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G134" s="37" t="inlineStr">
@@ -40293,11 +40325,11 @@
     </row>
     <row r="135">
       <c r="A135" s="37" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B135" s="37" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C135" s="37" t="inlineStr">
@@ -40328,11 +40360,11 @@
     </row>
     <row r="136">
       <c r="A136" s="37" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B136" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C136" s="37" t="inlineStr">
@@ -40363,11 +40395,11 @@
     </row>
     <row r="137">
       <c r="A137" s="37" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B137" s="37" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C137" s="37" t="inlineStr">
@@ -40398,11 +40430,11 @@
     </row>
     <row r="138">
       <c r="A138" s="37" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B138" s="37" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C138" s="37" t="inlineStr">
@@ -40433,11 +40465,11 @@
     </row>
     <row r="139">
       <c r="A139" s="37" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B139" s="37" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C139" s="37" t="inlineStr">
@@ -40468,11 +40500,11 @@
     </row>
     <row r="140">
       <c r="A140" s="37" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B140" s="37" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C140" s="37" t="inlineStr">
@@ -40503,11 +40535,11 @@
     </row>
     <row r="141">
       <c r="A141" s="37" t="n">
-        <v>86</v>
+        <v>2789</v>
       </c>
       <c r="B141" s="37" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C141" s="37" t="inlineStr">
@@ -40527,7 +40559,7 @@
       </c>
       <c r="F141" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G141" s="37" t="inlineStr">
@@ -40538,11 +40570,11 @@
     </row>
     <row r="142">
       <c r="A142" s="37" t="n">
-        <v>157</v>
+        <v>1942</v>
       </c>
       <c r="B142" s="37" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C142" s="37" t="inlineStr">
@@ -40562,7 +40594,7 @@
       </c>
       <c r="F142" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G142" s="37" t="inlineStr">
@@ -40573,11 +40605,11 @@
     </row>
     <row r="143">
       <c r="A143" s="37" t="n">
-        <v>2789</v>
+        <v>161</v>
       </c>
       <c r="B143" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C143" s="37" t="inlineStr">
@@ -40608,11 +40640,11 @@
     </row>
     <row r="144">
       <c r="A144" s="37" t="n">
-        <v>1942</v>
+        <v>110</v>
       </c>
       <c r="B144" s="37" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C144" s="37" t="inlineStr">
@@ -40622,17 +40654,17 @@
       </c>
       <c r="D144" s="37" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E144" s="37" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F144" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G144" s="37" t="inlineStr">
@@ -40643,11 +40675,11 @@
     </row>
     <row r="145">
       <c r="A145" s="37" t="n">
-        <v>161</v>
+        <v>1943</v>
       </c>
       <c r="B145" s="37" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C145" s="37" t="inlineStr">
@@ -40657,17 +40689,17 @@
       </c>
       <c r="D145" s="37" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>03/09/2026</t>
         </is>
       </c>
       <c r="E145" s="37" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F145" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G145" s="37" t="inlineStr">
@@ -40678,11 +40710,11 @@
     </row>
     <row r="146">
       <c r="A146" s="37" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="B146" s="37" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C146" s="37" t="inlineStr">
@@ -40713,11 +40745,11 @@
     </row>
     <row r="147">
       <c r="A147" s="37" t="n">
-        <v>1943</v>
+        <v>110</v>
       </c>
       <c r="B147" s="37" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C147" s="37" t="inlineStr">
@@ -40727,12 +40759,12 @@
       </c>
       <c r="D147" s="37" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E147" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F147" s="37" t="inlineStr">
@@ -40748,11 +40780,11 @@
     </row>
     <row r="148">
       <c r="A148" s="37" t="n">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="B148" s="37" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C148" s="37" t="inlineStr">
@@ -40762,12 +40794,12 @@
       </c>
       <c r="D148" s="37" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>04/09/2026</t>
         </is>
       </c>
       <c r="E148" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F148" s="37" t="inlineStr">
@@ -40783,11 +40815,11 @@
     </row>
     <row r="149">
       <c r="A149" s="37" t="n">
-        <v>110</v>
+        <v>2789</v>
       </c>
       <c r="B149" s="37" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C149" s="37" t="inlineStr">
@@ -40818,11 +40850,11 @@
     </row>
     <row r="150">
       <c r="A150" s="37" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B150" s="37" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C150" s="37" t="inlineStr">
@@ -40853,11 +40885,11 @@
     </row>
     <row r="151">
       <c r="A151" s="37" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B151" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C151" s="37" t="inlineStr">
@@ -40888,11 +40920,11 @@
     </row>
     <row r="152">
       <c r="A152" s="37" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B152" s="37" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C152" s="37" t="inlineStr">
@@ -40923,11 +40955,11 @@
     </row>
     <row r="153">
       <c r="A153" s="37" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B153" s="37" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C153" s="37" t="inlineStr">
@@ -40958,11 +40990,11 @@
     </row>
     <row r="154">
       <c r="A154" s="37" t="n">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B154" s="37" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C154" s="37" t="inlineStr">
@@ -40993,11 +41025,11 @@
     </row>
     <row r="155">
       <c r="A155" s="37" t="n">
-        <v>1996</v>
+        <v>1943</v>
       </c>
       <c r="B155" s="37" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C155" s="37" t="inlineStr">
@@ -41017,7 +41049,7 @@
       </c>
       <c r="F155" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G155" s="37" t="inlineStr">
@@ -41028,11 +41060,11 @@
     </row>
     <row r="156">
       <c r="A156" s="37" t="n">
-        <v>157</v>
+        <v>2789</v>
       </c>
       <c r="B156" s="37" t="inlineStr">
         <is>
-          <t>Walquiria Araujo Flores</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C156" s="37" t="inlineStr">
@@ -41052,7 +41084,7 @@
       </c>
       <c r="F156" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G156" s="37" t="inlineStr">
@@ -41063,11 +41095,11 @@
     </row>
     <row r="157">
       <c r="A157" s="37" t="n">
-        <v>1943</v>
+        <v>161</v>
       </c>
       <c r="B157" s="37" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C157" s="37" t="inlineStr">
@@ -41098,11 +41130,11 @@
     </row>
     <row r="158">
       <c r="A158" s="37" t="n">
-        <v>2789</v>
+        <v>1943</v>
       </c>
       <c r="B158" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C158" s="37" t="inlineStr">
@@ -41112,17 +41144,17 @@
       </c>
       <c r="D158" s="37" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E158" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F158" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G158" s="37" t="inlineStr">
@@ -41133,11 +41165,11 @@
     </row>
     <row r="159">
       <c r="A159" s="37" t="n">
-        <v>161</v>
+        <v>1943</v>
       </c>
       <c r="B159" s="37" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C159" s="37" t="inlineStr">
@@ -41147,12 +41179,12 @@
       </c>
       <c r="D159" s="37" t="inlineStr">
         <is>
-          <t>04/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="E159" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Terça</t>
         </is>
       </c>
       <c r="F159" s="37" t="inlineStr">
@@ -41182,12 +41214,12 @@
       </c>
       <c r="D160" s="37" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E160" s="37" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F160" s="37" t="inlineStr">
@@ -41203,11 +41235,11 @@
     </row>
     <row r="161">
       <c r="A161" s="37" t="n">
-        <v>1943</v>
+        <v>2789</v>
       </c>
       <c r="B161" s="37" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C161" s="37" t="inlineStr">
@@ -41217,17 +41249,17 @@
       </c>
       <c r="D161" s="37" t="inlineStr">
         <is>
-          <t>08/09/2026</t>
+          <t>09/09/2026</t>
         </is>
       </c>
       <c r="E161" s="37" t="inlineStr">
         <is>
-          <t>Terça</t>
+          <t>Quarta</t>
         </is>
       </c>
       <c r="F161" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G161" s="37" t="inlineStr">
@@ -41238,11 +41270,11 @@
     </row>
     <row r="162">
       <c r="A162" s="37" t="n">
-        <v>1943</v>
+        <v>149</v>
       </c>
       <c r="B162" s="37" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C162" s="37" t="inlineStr">
@@ -41273,11 +41305,11 @@
     </row>
     <row r="163">
       <c r="A163" s="37" t="n">
-        <v>2789</v>
+        <v>1996</v>
       </c>
       <c r="B163" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C163" s="37" t="inlineStr">
@@ -41308,11 +41340,11 @@
     </row>
     <row r="164">
       <c r="A164" s="37" t="n">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="B164" s="37" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C164" s="37" t="inlineStr">
@@ -41332,7 +41364,7 @@
       </c>
       <c r="F164" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G164" s="37" t="inlineStr">
@@ -41343,11 +41375,11 @@
     </row>
     <row r="165">
       <c r="A165" s="37" t="n">
-        <v>1996</v>
+        <v>1943</v>
       </c>
       <c r="B165" s="37" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="C165" s="37" t="inlineStr">
@@ -41367,7 +41399,7 @@
       </c>
       <c r="F165" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G165" s="37" t="inlineStr">
@@ -41378,11 +41410,11 @@
     </row>
     <row r="166">
       <c r="A166" s="37" t="n">
-        <v>110</v>
+        <v>2789</v>
       </c>
       <c r="B166" s="37" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C166" s="37" t="inlineStr">
@@ -41413,11 +41445,11 @@
     </row>
     <row r="167">
       <c r="A167" s="37" t="n">
-        <v>1943</v>
+        <v>1996</v>
       </c>
       <c r="B167" s="37" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C167" s="37" t="inlineStr">
@@ -41448,11 +41480,11 @@
     </row>
     <row r="168">
       <c r="A168" s="37" t="n">
-        <v>2789</v>
+        <v>110</v>
       </c>
       <c r="B168" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Anderson Jose de Santana</t>
         </is>
       </c>
       <c r="C168" s="37" t="inlineStr">
@@ -41462,17 +41494,17 @@
       </c>
       <c r="D168" s="37" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E168" s="37" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F168" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G168" s="37" t="inlineStr">
@@ -41483,11 +41515,11 @@
     </row>
     <row r="169">
       <c r="A169" s="37" t="n">
-        <v>1996</v>
+        <v>80</v>
       </c>
       <c r="B169" s="37" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Gisele Lopes Justiniano</t>
         </is>
       </c>
       <c r="C169" s="37" t="inlineStr">
@@ -41497,17 +41529,17 @@
       </c>
       <c r="D169" s="37" t="inlineStr">
         <is>
-          <t>09/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
       <c r="E169" s="37" t="inlineStr">
         <is>
-          <t>Quarta</t>
+          <t>Quinta</t>
         </is>
       </c>
       <c r="F169" s="37" t="inlineStr">
         <is>
-          <t>Tarde</t>
+          <t>Manhã</t>
         </is>
       </c>
       <c r="G169" s="37" t="inlineStr">
@@ -41518,11 +41550,11 @@
     </row>
     <row r="170">
       <c r="A170" s="37" t="n">
-        <v>110</v>
+        <v>2789</v>
       </c>
       <c r="B170" s="37" t="inlineStr">
         <is>
-          <t>Anderson Jose de Santana</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C170" s="37" t="inlineStr">
@@ -41553,11 +41585,11 @@
     </row>
     <row r="171">
       <c r="A171" s="37" t="n">
-        <v>80</v>
+        <v>149</v>
       </c>
       <c r="B171" s="37" t="inlineStr">
         <is>
-          <t>Gisele Lopes Justiniano</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="C171" s="37" t="inlineStr">
@@ -41588,11 +41620,11 @@
     </row>
     <row r="172">
       <c r="A172" s="37" t="n">
-        <v>2789</v>
+        <v>1942</v>
       </c>
       <c r="B172" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Rafael Ramos Recalde</t>
         </is>
       </c>
       <c r="C172" s="37" t="inlineStr">
@@ -41623,11 +41655,11 @@
     </row>
     <row r="173">
       <c r="A173" s="37" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="B173" s="37" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Rozana Reis da Silva</t>
         </is>
       </c>
       <c r="C173" s="37" t="inlineStr">
@@ -41658,11 +41690,11 @@
     </row>
     <row r="174">
       <c r="A174" s="37" t="n">
-        <v>1942</v>
+        <v>1996</v>
       </c>
       <c r="B174" s="37" t="inlineStr">
         <is>
-          <t>Rafael Ramos Recalde</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C174" s="37" t="inlineStr">
@@ -41693,11 +41725,11 @@
     </row>
     <row r="175">
       <c r="A175" s="37" t="n">
-        <v>161</v>
+        <v>86</v>
       </c>
       <c r="B175" s="37" t="inlineStr">
         <is>
-          <t>Rozana Reis da Silva</t>
+          <t>Silvina Regina de Souza Valiente</t>
         </is>
       </c>
       <c r="C175" s="37" t="inlineStr">
@@ -41728,11 +41760,11 @@
     </row>
     <row r="176">
       <c r="A176" s="37" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B176" s="37" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C176" s="37" t="inlineStr">
@@ -41763,11 +41795,11 @@
     </row>
     <row r="177">
       <c r="A177" s="37" t="n">
-        <v>86</v>
+        <v>2789</v>
       </c>
       <c r="B177" s="37" t="inlineStr">
         <is>
-          <t>Silvina Regina de Souza Valiente</t>
+          <t>Kariele Jackeline Rodrigues Silva</t>
         </is>
       </c>
       <c r="C177" s="37" t="inlineStr">
@@ -41787,7 +41819,7 @@
       </c>
       <c r="F177" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G177" s="37" t="inlineStr">
@@ -41812,12 +41844,12 @@
       </c>
       <c r="D178" s="37" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E178" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F178" s="37" t="inlineStr">
@@ -41833,11 +41865,11 @@
     </row>
     <row r="179">
       <c r="A179" s="37" t="n">
-        <v>2789</v>
+        <v>1996</v>
       </c>
       <c r="B179" s="37" t="inlineStr">
         <is>
-          <t>Kariele Jackeline Rodrigues Silva</t>
+          <t>Sara Eliane Talaveira de Oliveira</t>
         </is>
       </c>
       <c r="C179" s="37" t="inlineStr">
@@ -41847,12 +41879,12 @@
       </c>
       <c r="D179" s="37" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>11/09/2026</t>
         </is>
       </c>
       <c r="E179" s="37" t="inlineStr">
         <is>
-          <t>Quinta</t>
+          <t>Sexta</t>
         </is>
       </c>
       <c r="F179" s="37" t="inlineStr">
@@ -41868,11 +41900,11 @@
     </row>
     <row r="180">
       <c r="A180" s="37" t="n">
-        <v>1996</v>
+        <v>157</v>
       </c>
       <c r="B180" s="37" t="inlineStr">
         <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
+          <t>Walquiria Araujo Flores</t>
         </is>
       </c>
       <c r="C180" s="37" t="inlineStr">
@@ -41892,7 +41924,7 @@
       </c>
       <c r="F180" s="37" t="inlineStr">
         <is>
-          <t>Manhã</t>
+          <t>Tarde</t>
         </is>
       </c>
       <c r="G180" s="37" t="inlineStr">
@@ -41917,12 +41949,12 @@
       </c>
       <c r="D181" s="37" t="inlineStr">
         <is>
-          <t>11/09/2026</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E181" s="37" t="inlineStr">
         <is>
-          <t>Sexta</t>
+          <t>Segunda</t>
         </is>
       </c>
       <c r="F181" s="37" t="inlineStr">
@@ -41936,113 +41968,8 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="37" t="n">
-        <v>1996</v>
-      </c>
-      <c r="B182" s="37" t="inlineStr">
-        <is>
-          <t>Sara Eliane Talaveira de Oliveira</t>
-        </is>
-      </c>
-      <c r="C182" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D182" s="37" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E182" s="37" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F182" s="37" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G182" s="37" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="37" t="n">
-        <v>157</v>
-      </c>
-      <c r="B183" s="37" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C183" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D183" s="37" t="inlineStr">
-        <is>
-          <t>11/09/2026</t>
-        </is>
-      </c>
-      <c r="E183" s="37" t="inlineStr">
-        <is>
-          <t>Sexta</t>
-        </is>
-      </c>
-      <c r="F183" s="37" t="inlineStr">
-        <is>
-          <t>Tarde</t>
-        </is>
-      </c>
-      <c r="G183" s="37" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="37" t="n">
-        <v>157</v>
-      </c>
-      <c r="B184" s="37" t="inlineStr">
-        <is>
-          <t>Walquiria Araujo Flores</t>
-        </is>
-      </c>
-      <c r="C184" s="37" t="inlineStr">
-        <is>
-          <t>Equipe 4</t>
-        </is>
-      </c>
-      <c r="D184" s="37" t="inlineStr">
-        <is>
-          <t>31/08/2026</t>
-        </is>
-      </c>
-      <c r="E184" s="37" t="inlineStr">
-        <is>
-          <t>Segunda</t>
-        </is>
-      </c>
-      <c r="F184" s="37" t="inlineStr">
-        <is>
-          <t>Manhã</t>
-        </is>
-      </c>
-      <c r="G184" s="37" t="inlineStr">
-        <is>
-          <t>Sem visita registrada nesse turno — possível folga, atestado ou falta (confirmar com a escala)</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:G184"/>
+  <autoFilter ref="A2:G181"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>

--- a/data/historico/semanas_322-326.xlsx
+++ b/data/historico/semanas_322-326.xlsx
@@ -50733,47 +50733,47 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17761374</t>
+          <t>17604246</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Rua SANTO ANTONIO SR</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>30 - R</t>
+          <t>282 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:29</t>
+          <t>23/09/2026 15:12</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:58</t>
+          <t>23/09/2026 15:41</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -50783,47 +50783,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17604246</t>
+          <t>17761374</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua SANTO ANTONIO SR</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>282 - R</t>
+          <t>30 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:12</t>
+          <t>02/10/2026 15:29</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:41</t>
+          <t>02/10/2026 15:58</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">

--- a/data/historico/semanas_322-326.xlsx
+++ b/data/historico/semanas_322-326.xlsx
@@ -52233,47 +52233,47 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>17769628</t>
+          <t>17731458</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
+          <t>Rua JAMIL SALDANHA DERZI</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>506 - R</t>
+          <t>603 - 1 - TB</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:47</t>
+          <t>30/09/2026 14:25</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 16:11</t>
+          <t>30/09/2026 14:49</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -52283,47 +52283,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17731458</t>
+          <t>17769628</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua JAMIL SALDANHA DERZI</t>
+          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>603 - 1 - TB</t>
+          <t>506 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:25</t>
+          <t>01/10/2026 15:47</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:49</t>
+          <t>01/10/2026 16:11</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">

--- a/data/historico/semanas_322-326.xlsx
+++ b/data/historico/semanas_322-326.xlsx
@@ -50633,47 +50633,47 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>17746454</t>
+          <t>17761374</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>445 - JARDIM IVONE</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Rua ADEMIR P JUNIOR</t>
+          <t>Rua SANTO ANTONIO SR</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>47 - R</t>
+          <t>30 - R</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:15</t>
+          <t>02/10/2026 15:29</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:44</t>
+          <t>02/10/2026 15:58</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -50733,7 +50733,7 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
@@ -50743,37 +50743,37 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17604246</t>
+          <t>17746454</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>445 - JARDIM IVONE</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q033</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua ADEMIR P JUNIOR</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>282 - R</t>
+          <t>47 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:12</t>
+          <t>01/10/2026 15:15</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:41</t>
+          <t>01/10/2026 15:44</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -50783,47 +50783,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17761374</t>
+          <t>17604246</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua SANTO ANTONIO SR</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>30 - R</t>
+          <t>282 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:29</t>
+          <t>23/09/2026 15:12</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:58</t>
+          <t>23/09/2026 15:41</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
@@ -52233,47 +52233,47 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>17731458</t>
+          <t>17769628</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Rua JAMIL SALDANHA DERZI</t>
+          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>603 - 1 - TB</t>
+          <t>506 - R</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:25</t>
+          <t>01/10/2026 15:47</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:49</t>
+          <t>01/10/2026 16:11</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -52283,47 +52283,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17769628</t>
+          <t>17731458</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
+          <t>Rua JAMIL SALDANHA DERZI</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>506 - R</t>
+          <t>603 - 1 - TB</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:47</t>
+          <t>30/09/2026 14:25</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 16:11</t>
+          <t>30/09/2026 14:49</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">

--- a/data/historico/semanas_322-326.xlsx
+++ b/data/historico/semanas_322-326.xlsx
@@ -50633,47 +50633,47 @@
     <row r="37">
       <c r="A37" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Juliana Patricia Goncalves</t>
         </is>
       </c>
       <c r="B37" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C37" s="30" t="inlineStr">
         <is>
-          <t>17761374</t>
+          <t>17746454</t>
         </is>
       </c>
       <c r="D37" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>445 - JARDIM IVONE</t>
         </is>
       </c>
       <c r="E37" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q033</t>
         </is>
       </c>
       <c r="F37" s="29" t="inlineStr">
         <is>
-          <t>Rua SANTO ANTONIO SR</t>
+          <t>Rua ADEMIR P JUNIOR</t>
         </is>
       </c>
       <c r="G37" s="29" t="inlineStr">
         <is>
-          <t>30 - R</t>
+          <t>47 - R</t>
         </is>
       </c>
       <c r="H37" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:29</t>
+          <t>01/10/2026 15:15</t>
         </is>
       </c>
       <c r="I37" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:58</t>
+          <t>01/10/2026 15:44</t>
         </is>
       </c>
       <c r="J37" s="29" t="n">
@@ -50733,7 +50733,7 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Juliana Patricia Goncalves</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
@@ -50743,37 +50743,37 @@
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17746454</t>
+          <t>17604246</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>445 - JARDIM IVONE</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q033</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Rua ADEMIR P JUNIOR</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>47 - R</t>
+          <t>282 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:15</t>
+          <t>23/09/2026 15:12</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:44</t>
+          <t>23/09/2026 15:41</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -50783,47 +50783,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17604246</t>
+          <t>17761374</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua SANTO ANTONIO SR</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>282 - R</t>
+          <t>30 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:12</t>
+          <t>02/10/2026 15:29</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:41</t>
+          <t>02/10/2026 15:58</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
@@ -52233,47 +52233,47 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>17769628</t>
+          <t>17731458</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
+          <t>Rua JAMIL SALDANHA DERZI</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>506 - R</t>
+          <t>603 - 1 - TB</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:47</t>
+          <t>30/09/2026 14:25</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 16:11</t>
+          <t>30/09/2026 14:49</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -52283,47 +52283,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17731458</t>
+          <t>17769628</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua JAMIL SALDANHA DERZI</t>
+          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>603 - 1 - TB</t>
+          <t>506 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:25</t>
+          <t>01/10/2026 15:47</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:49</t>
+          <t>01/10/2026 16:11</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">

--- a/data/historico/semanas_322-326.xlsx
+++ b/data/historico/semanas_322-326.xlsx
@@ -50733,47 +50733,47 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17604246</t>
+          <t>17761374</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua SANTO ANTONIO SR</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>282 - R</t>
+          <t>30 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:12</t>
+          <t>02/10/2026 15:29</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:41</t>
+          <t>02/10/2026 15:58</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -50783,47 +50783,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17761374</t>
+          <t>17604246</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua SANTO ANTONIO SR</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>30 - R</t>
+          <t>282 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:29</t>
+          <t>23/09/2026 15:12</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:58</t>
+          <t>23/09/2026 15:41</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
@@ -52233,47 +52233,47 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>17731458</t>
+          <t>17769628</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Rua JAMIL SALDANHA DERZI</t>
+          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>603 - 1 - TB</t>
+          <t>506 - R</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:25</t>
+          <t>01/10/2026 15:47</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:49</t>
+          <t>01/10/2026 16:11</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -52283,47 +52283,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17769628</t>
+          <t>17731458</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
+          <t>Rua JAMIL SALDANHA DERZI</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>506 - R</t>
+          <t>603 - 1 - TB</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:47</t>
+          <t>30/09/2026 14:25</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 16:11</t>
+          <t>30/09/2026 14:49</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">

--- a/data/historico/semanas_322-326.xlsx
+++ b/data/historico/semanas_322-326.xlsx
@@ -50733,47 +50733,47 @@
     <row r="39">
       <c r="A39" s="29" t="inlineStr">
         <is>
-          <t>Ana Gabriela Silva Garcete</t>
+          <t>Kátia Cilene Silveira Machado</t>
         </is>
       </c>
       <c r="B39" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 4</t>
         </is>
       </c>
       <c r="C39" s="30" t="inlineStr">
         <is>
-          <t>17761374</t>
+          <t>17604246</t>
         </is>
       </c>
       <c r="D39" s="29" t="inlineStr">
         <is>
-          <t>401 - EMÍLIO DIAS BRANDÃO</t>
+          <t>443 - KAMEL SAAD 1</t>
         </is>
       </c>
       <c r="E39" s="29" t="inlineStr">
         <is>
-          <t>Q008</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F39" s="29" t="inlineStr">
         <is>
-          <t>Rua SANTO ANTONIO SR</t>
+          <t>Rua SALIM DERZI</t>
         </is>
       </c>
       <c r="G39" s="29" t="inlineStr">
         <is>
-          <t>30 - R</t>
+          <t>282 - R</t>
         </is>
       </c>
       <c r="H39" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:29</t>
+          <t>23/09/2026 15:12</t>
         </is>
       </c>
       <c r="I39" s="29" t="inlineStr">
         <is>
-          <t>02/10/2026 15:58</t>
+          <t>23/09/2026 15:41</t>
         </is>
       </c>
       <c r="J39" s="29" t="n">
@@ -50783,47 +50783,47 @@
     <row r="40">
       <c r="A40" s="29" t="inlineStr">
         <is>
-          <t>Kátia Cilene Silveira Machado</t>
+          <t>Ana Gabriela Silva Garcete</t>
         </is>
       </c>
       <c r="B40" s="29" t="inlineStr">
         <is>
-          <t>Equipe 4</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C40" s="30" t="inlineStr">
         <is>
-          <t>17604246</t>
+          <t>17761374</t>
         </is>
       </c>
       <c r="D40" s="29" t="inlineStr">
         <is>
-          <t>443 - KAMEL SAAD 1</t>
+          <t>401 - EMÍLIO DIAS BRANDÃO</t>
         </is>
       </c>
       <c r="E40" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q008</t>
         </is>
       </c>
       <c r="F40" s="29" t="inlineStr">
         <is>
-          <t>Rua SALIM DERZI</t>
+          <t>Rua SANTO ANTONIO SR</t>
         </is>
       </c>
       <c r="G40" s="29" t="inlineStr">
         <is>
-          <t>282 - R</t>
+          <t>30 - R</t>
         </is>
       </c>
       <c r="H40" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:12</t>
+          <t>02/10/2026 15:29</t>
         </is>
       </c>
       <c r="I40" s="29" t="inlineStr">
         <is>
-          <t>23/09/2026 15:41</t>
+          <t>02/10/2026 15:58</t>
         </is>
       </c>
       <c r="J40" s="29" t="n">
@@ -52233,47 +52233,47 @@
     <row r="69">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>Wagner Tarlei Gomes</t>
+          <t>Miglidiane Maciel Ajala</t>
         </is>
       </c>
       <c r="B69" s="29" t="inlineStr">
         <is>
-          <t>Equipe 1</t>
+          <t>Equipe 3</t>
         </is>
       </c>
       <c r="C69" s="30" t="inlineStr">
         <is>
-          <t>17769628</t>
+          <t>17731458</t>
         </is>
       </c>
       <c r="D69" s="29" t="inlineStr">
         <is>
-          <t>400 - JULIA CARDINAL</t>
+          <t>425 - JARDIM ESTORIL</t>
         </is>
       </c>
       <c r="E69" s="29" t="inlineStr">
         <is>
-          <t>Q018</t>
+          <t>Q015</t>
         </is>
       </c>
       <c r="F69" s="29" t="inlineStr">
         <is>
-          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
+          <t>Rua JAMIL SALDANHA DERZI</t>
         </is>
       </c>
       <c r="G69" s="29" t="inlineStr">
         <is>
-          <t>506 - R</t>
+          <t>603 - 1 - TB</t>
         </is>
       </c>
       <c r="H69" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 15:47</t>
+          <t>30/09/2026 14:25</t>
         </is>
       </c>
       <c r="I69" s="29" t="inlineStr">
         <is>
-          <t>01/10/2026 16:11</t>
+          <t>30/09/2026 14:49</t>
         </is>
       </c>
       <c r="J69" s="29" t="n">
@@ -52283,47 +52283,47 @@
     <row r="70">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>Miglidiane Maciel Ajala</t>
+          <t>Wagner Tarlei Gomes</t>
         </is>
       </c>
       <c r="B70" s="29" t="inlineStr">
         <is>
-          <t>Equipe 3</t>
+          <t>Equipe 1</t>
         </is>
       </c>
       <c r="C70" s="30" t="inlineStr">
         <is>
-          <t>17731458</t>
+          <t>17769628</t>
         </is>
       </c>
       <c r="D70" s="29" t="inlineStr">
         <is>
-          <t>425 - JARDIM ESTORIL</t>
+          <t>400 - JULIA CARDINAL</t>
         </is>
       </c>
       <c r="E70" s="29" t="inlineStr">
         <is>
-          <t>Q015</t>
+          <t>Q018</t>
         </is>
       </c>
       <c r="F70" s="29" t="inlineStr">
         <is>
-          <t>Rua JAMIL SALDANHA DERZI</t>
+          <t>Rua MARIA TRINDADE DE OLIVEIRA</t>
         </is>
       </c>
       <c r="G70" s="29" t="inlineStr">
         <is>
-          <t>603 - 1 - TB</t>
+          <t>506 - R</t>
         </is>
       </c>
       <c r="H70" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:25</t>
+          <t>01/10/2026 15:47</t>
         </is>
       </c>
       <c r="I70" s="29" t="inlineStr">
         <is>
-          <t>30/09/2026 14:49</t>
+          <t>01/10/2026 16:11</t>
         </is>
       </c>
       <c r="J70" s="29" t="n">
